--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340a535ec0c84cac</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,94 +846,94 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c4bead3a549cf5d</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>Humana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=340a535ec0c84cac</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Terraform MLOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ae79047ff46576a5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Practicing Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa3ba1c1eb894e8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,89 +1126,89 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer-Audience Data Platform</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
@@ -1243,20 +1243,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>MLOps</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1287,11 +1287,11 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Data Engineer-Audience Data Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,137 +1441,137 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47565bba5f358319</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67847e8511f65c7d</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58a2dfa4262a025</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Docker MLOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,94 +1581,94 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc646fda2eb85619</t>
+          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aedb8b8aec3e159</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c7d8b9629dc69f</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6084426de3e80dd2</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e96f433128edfd7d</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa10ecda14dd22ca</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24f30709341ff2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,217 +1816,217 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5bd814d339eaf</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a58e6f90fd69fc</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=526d2298d07834e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4955b1f3fc7acab</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94a1e695d6167042</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdf14ce4e3b4d297</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Kubernetes MLOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b07ea23f99e54254</t>
+          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Billings, MT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c4855052460f6e5</t>
+          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Associate ML Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0a3a892faea7852</t>
+          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2127,81 +2127,81 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dbbd9b8557c4ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer - Remote, USA</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bluelight Consulting</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Informatica PowerCenter, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9db3d7325c656bcd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer, DataOps &amp; Platform Services</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Anheuser-Busch</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=3726b62a784e7a79</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>GCP Solution Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=606fbcf8c540193f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>San Ramon, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Berkshire Hathaway Specialty Insurance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, DataOps &amp; Platform Services</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Anheuser-Busch</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3726b62a784e7a79</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>JCL Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Advancement Technical Systems Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>The Nehr Agency</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,252 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Availity, LLC.</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>The Nehr Agency</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>JCL Developer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Advancement Technical Systems Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Syracuse University</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Terraform MLOps Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, MLOps, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14ef9a02e63046b1</t>
+          <t>https://www.indeed.com/viewjob?jk=ae79047ff46576a5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Practicing Data Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f80931732d91d4a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa3ba1c1eb894e8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae79047ff46576a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Practicing Data Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,69 +1081,69 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa3ba1c1eb894e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MLOps</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Spark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09a09d113d12e316</t>
+          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer-Audience Data Platform</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Docker MLOps Engineer</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Databricks, Spark, Scala, Snowflake, Cassandra, Tableau, Splunk, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddc72cf3e9f4cacd</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Sigma Computing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Kubernetes MLOps Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6327e72675e4d0</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73fcdf60543dc29</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate ML Infrastructure Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=714ec340c93e2f35</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer, DataOps &amp; Platform Services</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Anheuser-Busch</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, DataOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=3726b62a784e7a79</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,94 +2421,94 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>GCP Solution Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=606fbcf8c540193f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, DataOps &amp; Platform Services</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Anheuser-Busch</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3726b62a784e7a79</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GCP Solution Architect</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606fbcf8c540193f</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Ramon, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612df1868af9d54f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Scientist / Senior Data Scientist (Risk Modeling Focus)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway Specialty Insurance</t>
+          <t>The Nehr Agency</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Docker, Git, Python</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dcb545f058b93</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Advancement Technical Systems Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,367 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Infrastructure</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>AI/LLM Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Availity, LLC.</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Data Support Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Sumitomo Group</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>GenAI Threat Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Oracle, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57347e70ea0f51d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>JCL Developer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b79a0aab80d0133</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Advancement Technical Systems Developer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Syracuse University</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>The Nehr Agency</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Humana</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Google Cloud Platform, Scala, Kafka, Snowflake, Oracle, SQL Server, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=340a535ec0c84cac</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,19 +1301,19 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
@@ -1483,25 +1483,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Software Engineer II, Search &amp; Recs</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1325be40d902ff</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
@@ -2288,17 +2288,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, DataOps &amp; Platform Services</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Anheuser-Busch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, DataOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3726b62a784e7a79</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
         </is>
       </c>
     </row>
@@ -2947,6 +2947,41 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>The Nehr Agency</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,25 +678,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,59 +1056,59 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer-Audience Data Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,77 +1466,77 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer II, Search &amp; Recs</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,19 +1616,19 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1325be40d902ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Software Engineer II, Search &amp; Recs</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1325be40d902ff</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>SALOMON</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Security Engineer II – Cloud &amp; Data Security</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Sigma Computing</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Databricks, GCP, BigQuery, Spark, Scala, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f71b276dda5b6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,69 +2236,69 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>BITS, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GCP Solution Architect</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606fbcf8c540193f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>GCP Solution Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=606fbcf8c540193f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,42 +2551,42 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,24 +2796,24 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2836,29 +2836,29 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Advancement Technical Systems Developer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Availity, LLC.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,17 +2971,192 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Advancement Technical Systems Developer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Syracuse University</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Syracuse, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>The Nehr Agency</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Progressive Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Merrifield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>InformAI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae79047ff46576a5</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae79047ff46576a5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Togetherwork</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer-Audience Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer-Audience Data Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II, Search &amp; Recs</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,19 +1686,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1325be40d902ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SALOMON</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=591cf05ec928c921</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Software Engineer II, Search &amp; Recs</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Wayfair</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=3b1325be40d902ff</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>datAvail</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=49c55bb99b922dcc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Selenium Automation Tester</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>ASTRELUX IT INC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=3299fc75914979c2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1ffba260a42149a</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BITS, Inc.</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Software Development Intern</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee7bab82316f7860</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>SPIGEN Inc. Multi-Position</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>KOTRA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf57e231909db50</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GCP Solution Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606fbcf8c540193f</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>BITS, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,42 +2621,42 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Backend Developer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Sedgwick</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e334b20b2a1ff39</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>GCP Solution Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=606fbcf8c540193f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,94 +2771,94 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI/LLM Engineer</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Availity, LLC.</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Advancement Technical Systems Developer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AI/LLM Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Associate Data Solutions Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Merrifield, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,15 +3146,330 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43f6a37b9cf1857f</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Cloud Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Fueled</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Advancement Technical Systems Developer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Syracuse University</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Syracuse, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Availity, LLC.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=15642f633949cc32</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>The Nehr Agency</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Progressive Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Merrifield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
         </is>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,52 +503,52 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer III</t>
+          <t>Software Engineer III - Databricks / IAM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stellix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Foxborough, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23da0426139b73c0</t>
+          <t>https://www.indeed.com/viewjob?jk=43ad258f03ca42af</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Level - Connected Systems</t>
+          <t>Senior Data Engineer III</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pratt Miller</t>
+          <t>Stellix</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Foxborough, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,42 +556,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e51e277a7646929</t>
+          <t>https://www.indeed.com/viewjob?jk=23da0426139b73c0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer Sr Level - Connected Systems</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FusionStak LLC</t>
+          <t>Pratt Miller</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3092577afd5b3438</t>
+          <t>https://www.indeed.com/viewjob?jk=0e51e277a7646929</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>FusionStak LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Databricks</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a3d37ec6e3c854</t>
+          <t>https://www.indeed.com/viewjob?jk=3092577afd5b3438</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Databricks</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=48a3d37ec6e3c854</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>InformAI</t>
+          <t>The Brite Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86fc1393dcf5eb4a</t>
+          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Practicing Data Architect</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa3ba1c1eb894e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,102 +1056,102 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae79047ff46576a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect (Hybrid - Austin, TX)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Togetherwork</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, IAM, RDS, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=772798db531882c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer-Audience Data Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer-Audience Data Platform</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer II, Search &amp; Recs</t>
+          <t>Kubernetes ML Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Wayfair</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Google Cloud Platform, GCP, Vertex AI, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b1325be40d902ff</t>
+          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>datAvail</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49c55bb99b922dcc</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,77 +2166,77 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Selenium Automation Tester</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ASTRELUX IT INC</t>
+          <t>BITS, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Oracle, SQL Server, ETL, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3299fc75914979c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,67 +2351,67 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Intern</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, SQL Server, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee7bab82316f7860</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SPIGEN Inc. Multi-Position</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KOTRA</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf57e231909db50</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BITS, Inc.</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2512,11 +2512,11 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,137 +2666,137 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Backend Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Sedgwick</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e334b20b2a1ff39</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GCP Solution Architect</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, NoSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=606fbcf8c540193f</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,59 +2806,59 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>The Nehr Agency</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>Progressive Technology Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Merrifield, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Advancement Technical Systems Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,542 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Infrastructure</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Support Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Sumitomo Group</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>AI/LLM Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd5db90dd63e1bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Associate Data Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Boeing</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, ETL, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43f6a37b9cf1857f</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Cloud Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Fueled</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Terraform, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3847663034b7777f</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Advancement Technical Systems Developer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Syracuse University</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Availity, LLC.</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Kafka, Oracle, MySQL, Splunk, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eb91c6ddf5dcc6bd</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>ERP &amp; Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Missouri State University</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=15642f633949cc32</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>The Nehr Agency</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Progressive Technology Solutions</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Merrifield, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=b31ef1251547b795</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,104 +1046,104 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer-Audience Data Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=71b07c377b250f81</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer-Audience Data Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Kubernetes ML Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127254c89307645a</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Back-End AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>RightRev</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,42 +2166,42 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BITS, Inc.</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>BITS, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,29 +2446,29 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Development Engineer in Test II</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Collibra</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Alabama, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb45c1718469a28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Merrifield, VA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Advancement Technical Systems Developer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,332 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Advancement Technical Systems Developer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Syracuse University</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Syracuse, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>The Nehr Agency</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Backend Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Progressive Technology Solutions</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Merrifield, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, DynamoDB, CI/CD, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9dc5391680bb152</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer-Audience Data Platform</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Sr. Data Engineer-Audience Data Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
         </is>
       </c>
     </row>
@@ -1553,17 +1553,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Oracle APEX Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Softnice</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Back-End AI Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RightRev</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Vertex AI, Scala, Snowflake, Streams/Tasks, dbt, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1213278b93e6bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BITS, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>BITS, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,69 +2691,69 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test II</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Collibra</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Alabama, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb45c1718469a28</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Software Development Engineer in Test II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Collibra</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alabama, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=4fb45c1718469a28</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Advancement Technical Systems Developer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,15 +3251,85 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Advancement Technical Systems Developer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Syracuse University</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Syracuse, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, SQS, SNS, DynamoDB, CI/CD, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9dc5391680bb152</t>
         </is>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31ef1251547b795</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Network IoT Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=b31ef1251547b795</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e082ad2ab8b61482</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Sr. Data Engineer-Audience Data Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
+          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,19 +1441,19 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer-Audience Data Platform</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,29 +2516,29 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, SQS, SNS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2d800fdf55a09</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BITS, Inc.</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, MLOps, MLflow, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7a0685b33151974</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test II</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Collibra</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Alabama, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb45c1718469a28</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Advancement Technical Systems Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
         </is>
       </c>
     </row>
@@ -3198,17 +3198,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Java CI/CD Automation Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Progressive Technology Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Merrifield, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,120 +3216,15 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Power BI, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, DynamoDB, CI/CD, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0a853e0ae22d5c66</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Advancement Technical Systems Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Syracuse University</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Java CI/CD Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, DynamoDB, CI/CD, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9dc5391680bb152</t>
         </is>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b07c377b250f81</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=71b07c377b250f81</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer-Audience Data Platform</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Redshift, S3, ECS, Databricks, BigQuery, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f586df953aed9dc</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
@@ -1833,17 +1833,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
@@ -2498,17 +2498,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, SQS, SNS, RDS, Scala, DynamoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2d800fdf55a09</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, SQS, SNS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=35a2d800fdf55a09</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Software Engineer, Infrastructure</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Advancement Technical Systems Developer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
@@ -3163,17 +3163,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Nehr Agency</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Scala, NoSQL, Maven, Terraform, Git, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f3f3ed6f9ca8e1f</t>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>Advancement Technical Systems Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,50 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, Lambda, S3, SQS, SNS, DynamoDB, CI/CD, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b9dc5391680bb152</t>
         </is>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Brite Group</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fe4fefddbc3bf0</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Network IoT Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, SQS, SNS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31ef1251547b795</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer - CETS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Wheels Up</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,77 +1326,77 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71b07c377b250f81</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SpotOn</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28affa5b8f92c154</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
         </is>
       </c>
     </row>
@@ -1453,12 +1453,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Specialist, Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,94 +1616,94 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Oracle APEX Developer</t>
+          <t>Business Architect - Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Softnice</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f99ee94588d96c51</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
@@ -2463,17 +2463,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, SQS, SNS, RDS, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35a2d800fdf55a09</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Sr. Data Quality Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>WeVision LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Infrastructure</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, MySQL, MongoDB, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee844d3954d72d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3116,29 +3116,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Advancement Technical Systems Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,87 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Advancement Technical Systems Developer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Syracuse University</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Java CI/CD Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, DynamoDB, CI/CD, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b9dc5391680bb152</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Data Engineer Mid-Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Musco Sports Lighting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Urbandale, IA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - CETS</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,17 +1186,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9de3e03dd9f36515</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SpotOn</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Kafka, Snowflake, PostgreSQL, MongoDB, ETL</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb184a441994d14</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,69 +1501,69 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Specialist, Data Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, ETL, CI/CD</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c8452bdf60974b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Business Architect - Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Business Architect - Analytics Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,17 +1921,17 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,77 +2236,77 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Data Quality Engineer</t>
+          <t>Senior Engineer – Software Development</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WeVision LLC</t>
+          <t>Suvida Healthcare</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hive, Spark, Scala, Snowflake, ETL, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c60c23da97c691</t>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Tech-assist</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>ERP &amp; Database Systems Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Missouri State University</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks / IAM</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Hadoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,42 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ad258f03ca42af</t>
+          <t>https://www.indeed.com/viewjob?jk=27398865f051a625</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer III</t>
+          <t>Software Engineer III - Databricks / IAM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stellix</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Foxborough, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23da0426139b73c0</t>
+          <t>https://www.indeed.com/viewjob?jk=43ad258f03ca42af</t>
         </is>
       </c>
     </row>
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FusionStak LLC</t>
+          <t>Excel Global Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3092577afd5b3438</t>
+          <t>https://www.indeed.com/viewjob?jk=91b4973510591f22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, IAM, RDS, Azure, Databricks</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48a3d37ec6e3c854</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer Mid-Senior</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer Mid-Senior</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Musco Sports Lighting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Urbandale, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b4d2d88b717b0b6</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,59 +1196,59 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wheels Up</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,112 +1326,112 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, MySQL, MongoDB, NoSQL, ELT, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e4cb81ca830b19a</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Point Digital Finance</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=e981dee8a8957f52</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Business Architect - Analytics Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
+          <t>https://www.indeed.com/viewjob?jk=4f72ebd3e533588c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,137 +1686,137 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,19 +1826,19 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1847,81 +1847,81 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Business Architect - Analytics Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed03160ce6390bf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=4835794258ba535e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,77 +2236,77 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=6463453c55c50555</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,102 +2316,102 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,207 +2421,207 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Developer (Backend / Systems)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Grayson College</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denison, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,207 +2666,207 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Big Data Engineer | USA (Remote) | Virtual Interview | 10+ Years Experience</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tech-assist</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Hadoop, Hive, Oozie, Spark, Scala, Kafka, Data Modeling, Tableau</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba36279cfaab4a75</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ERP &amp; Database Systems Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Missouri State University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,172 +2876,172 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,112 +3086,847 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=fd73e974849ca1de</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nexus Cognitive Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3634d9eb507b99</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TomorrowNow</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>CAMP Facility Services</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Engineer – Software Development</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Suvida Healthcare</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data QA Engineer III</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Preferred Travel Group</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Lake, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Ibotta</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Dorman Products</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Colmar, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e93f0784efda3b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AWS Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Hitachi Digital Services</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB, Terraform</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a4f447ae01cd88d</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AWS Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Hitachi Digital Services</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB, Terraform</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=237a7b0a4e379a69</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Support Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Sumitomo Group</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>Advancement Technical Systems Developer</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>Syracuse University</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>Syracuse, NY, US USA</t>
         </is>
       </c>
-      <c r="D79" t="n">
+      <c r="D99" t="n">
         <v>10.4</v>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F99" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Java CI/CD Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, DynamoDB, CI/CD, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49d0e12bb989e139</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,17 +1483,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e981dee8a8957f52</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=e981dee8a8957f52</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f72ebd3e533588c</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=4f72ebd3e533588c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,67 +1756,67 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Business Architect - Analytics Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Platform Engineer (Remote / Contract)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Verve for Advertisers</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Site Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Digital Charter, Inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Architect - Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed03160ce6390bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,24 +2201,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835794258ba535e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6463453c55c50555</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr, Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Fusable</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=642c677020ee17d9</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed03160ce6390bf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=4835794258ba535e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=6463453c55c50555</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Developer (Backend / Systems)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Grayson College</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denison, TX, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c61070e2529052c</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,164 +2701,164 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Analyst - Custom Software</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Spark Business Works</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kalamazoo, MI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,24 +3006,24 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd73e974849ca1de</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nexus Cognitive Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3634d9eb507b99</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>eOne Infotech</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Engineer – Software Development</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Suvida Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, PostgreSQL, MongoDB, NoSQL, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f78e35d3201dd7</t>
+          <t>https://www.indeed.com/viewjob?jk=fd73e974849ca1de</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Senior Technical Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Nexus Cognitive Technologies</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,42 +3286,42 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=2e3634d9eb507b99</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,164 +3331,164 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e93f0784efda3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS Full Stack Developer</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB, Terraform</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a4f447ae01cd88d</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS Full Stack Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Hitachi Digital Services</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, DynamoDB, Terraform</t>
+          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=237a7b0a4e379a69</t>
+          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ERP &amp; Database Systems Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Missouri State University</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=0e93f0784efda3b0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3816,29 +3816,29 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Advancement Technical Systems Developer</t>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Java CI/CD Automation Engineer</t>
+          <t>ERP &amp; Database Systems Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Missouri State University</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, DynamoDB, CI/CD, Jenkins, Maven, Jenkins</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,112 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49d0e12bb989e139</t>
+          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>DLRdmv</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Advancement Technical Systems Developer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Syracuse University</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Syracuse, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GCP Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Excel Global Solutions</t>
+          <t>NeoGenomics</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ramsey, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,94 +636,94 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91b4973510591f22</t>
+          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>NeoGenomics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer Mid-Senior</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Data Engineer Mid-Senior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,42 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,69 +1221,69 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,24 +1291,24 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Point Digital Finance</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Snowflake, Data Modeling, Dimensional Modeling, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88c572a3f85eb53</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, SQS, SNS, IAM, RDS, Scala, PostgreSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=332e9fb32e0415f5</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Scala, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e981dee8a8957f52</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Java Trainer / Mentor / Educator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=4f72ebd3e533588c</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f72ebd3e533588c</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,104 +1781,104 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Business Architect - Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,112 +1956,112 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Platform Engineer (Remote / Contract)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Verve for Advertisers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Dataflow, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc3eada72d656f7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer (SRE)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Digital Charter, Inc</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28562b84d193894f</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quality Engineer – BDD Implementation (Data Ingestion &amp; Pipeline)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Snowflake, ETL, ELT, CI/CD, Jenkins, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8cfcc24a34054e</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Business Architect - Analytics Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Developer in Test - SDET</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Spark, Scala, Kafka, ETL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1adbd6944b89ed</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2074ca8a90ba86</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr, Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fusable</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=642c677020ee17d9</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr, Dev Ops Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fusable</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642c677020ee17d9</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed03160ce6390bf</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835794258ba535e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6463453c55c50555</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed03160ce6390bf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=4835794258ba535e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,42 +2656,42 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=6463453c55c50555</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,94 +2771,94 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4874398fdff6c74</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Analyst - Custom Software</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Spark Business Works</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kalamazoo, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ddc0a0e690c6c5</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>IT Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,24 +2971,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AI Integration Consultant</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, DynamoDB, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=fd73e974849ca1de</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Mid–Senior Level) – AWS &amp; Streaming</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>eOne Infotech</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Spark, PySpark, Scala, Kafka, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aaee4d4db3b4f0b</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data QA Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Preferred Travel Group</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,182 +3216,182 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd73e974849ca1de</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Technical Architect</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nexus Cognitive Technologies</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Spark, Scala, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e3634d9eb507b99</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=0e93f0784efda3b0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>ERP &amp; Database Systems Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Missouri State University</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e93f0784efda3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Teradata Developer-2</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,252 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>ERP &amp; Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Missouri State University</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>SQL Developer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>DLRdmv</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Advancement Technical Systems Developer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Syracuse University</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, ETL, Tableau, Git, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=079fe1b4f4ba9f8f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Level - Connected Systems</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Pratt Miller</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e51e277a7646929</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Engineer Sr Level - Connected Systems</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NeoGenomics</t>
+          <t>Pratt Miller</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ramsey, NJ, US USA</t>
+          <t>Huntersville, NC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
+          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
+          <t>https://www.indeed.com/viewjob?jk=0e51e277a7646929</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Myers, FL, US USA</t>
+          <t>Ramsey, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
+          <t>https://www.indeed.com/viewjob?jk=761c2dcb68dd2dfc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>NeoGenomics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Fort Myers, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Azure, Hive, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7940d8c5c6d10af4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer Mid-Senior</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Data Engineer Mid-Senior</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,59 +1091,59 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,59 +1256,59 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,104 +1501,104 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Java Trainer / Mentor / Educator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f72ebd3e533588c</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,17 +1711,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
@@ -1798,52 +1798,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Business Architect - Analytics Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Business Architect - Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PNC Financial Services Group</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
         </is>
       </c>
     </row>
@@ -2013,12 +2013,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Developer in Test - SDET</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2074ca8a90ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr, Dev Ops Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Fusable</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642c677020ee17d9</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Developer in Test - SDET</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2074ca8a90ba86</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr, Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Fusable</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=642c677020ee17d9</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed03160ce6390bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835794258ba535e</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6463453c55c50555</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed03160ce6390bf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4835794258ba535e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Identity AI / ML Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=6463453c55c50555</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IT Platform Engineer Senior</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Power BI, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c1b2de67639d71f</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI Integration Consultant</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, Scala, DynamoDB, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd73e974849ca1de</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data QA Engineer III</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Preferred Travel Group</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, ETL, ELT, Power BI, Tableau, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=587fd1c533e6509d</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Dorman Products</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colmar, PA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fountain House</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,17 +3391,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e93f0784efda3b0</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3787de0a39dc88</t>
         </is>
       </c>
     </row>
@@ -3478,17 +3478,17 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ERP &amp; Database Systems Engineer</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Missouri State University</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>ERP &amp; Database Systems Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DLRdmv</t>
+          <t>Missouri State University</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,15 +3776,50 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
         </is>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks / IAM</t>
+          <t>Senior Engineer - Software Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Northwestern Mutual</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, IAM, RDS, Databricks, Unity Catalog, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ad258f03ca42af</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d4b89b3a60512a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Software Engineer III - Databricks / IAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
+          <t>https://www.indeed.com/viewjob?jk=43ad258f03ca42af</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer Sr Level - Connected Systems</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Pratt Miller</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Huntersville, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e51e277a7646929</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AmaWaterways</t>
+          <t>CleanSlate Technology Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Calabasas, CA, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
+          <t>AWS, Glue, Kinesis, Azure, Databricks, Spark, Scala, Kafka, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
+          <t>https://www.indeed.com/viewjob?jk=464d15de6f80cd60</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer Mid-Senior</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>AmaWaterways</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Calabasas, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec6050907c5aa7a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Data Engineer Mid-Senior</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,77 +906,77 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior DevSecOps Engineer - Vilnius, Lithuania</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure, Blob Storage</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=30f293139b417c7f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,119 +1126,119 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
@@ -1322,11 +1322,11 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,49 +1371,49 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,112 +1571,112 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,129 +1861,129 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Business Architect - Analytics Engineer</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PNC Financial Services Group</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, MySQL, MongoDB, NoSQL, MLflow, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfef7aface75172</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,67 +2141,67 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=dfaa8ce7652f89e0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Developer in Test - SDET</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2074ca8a90ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c7bc8bfe481d5f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr, Dev Ops Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fusable</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
+          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642c677020ee17d9</t>
+          <t>https://www.indeed.com/viewjob?jk=07e7dfcc20e69935</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Software Developer in Test - SDET</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2074ca8a90ba86</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Sr, Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fusable</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed03160ce6390bf</t>
+          <t>https://www.indeed.com/viewjob?jk=642c677020ee17d9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4835794258ba535e</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Identity AI / ML Engineer</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,252 +2726,252 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, MLOps, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6463453c55c50555</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,94 +2981,94 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,137 +3191,137 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr. Cloud Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dorman Products</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Colmar, PA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Scala, GitHub Actions, Azure DevOps, Terraform, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad4a65f5253bb1f7</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Senior Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Fountain House</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3787de0a39dc88</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,54 +3436,54 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3492,11 +3492,11 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,59 +3506,59 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Lake, MS, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ERP &amp; Database Systems Engineer</t>
+          <t>Senior Data Systems Analyst</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Missouri State University</t>
+          <t>Fountain House</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
+          <t>https://www.indeed.com/viewjob?jk=bd3787de0a39dc88</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>DLRdmv</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Teradata Developer-2</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,365 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst (171972)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>FDE-Priniciple Software Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>DLRdmv</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Teradata Developer-2</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
           <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
         </is>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,70 +573,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III - Databricks / IAM</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43ad258f03ca42af</t>
+          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>TowneBank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, RDS, Azure, Cloud Storage, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Kafka, Time Travel, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b33992f847413ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9ae768345f66d696</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer - Vilnius, Lithuania</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure, Blob Storage</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f293139b417c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior DevSecOps Engineer - Vilnius, Lithuania</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure, Blob Storage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=30f293139b417c7f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24bf71f6d124c7ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1238,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,207 +1651,207 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,102 +2071,102 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,207 +2176,207 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfaa8ce7652f89e0</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c7bc8bfe481d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e7dfcc20e69935</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,137 +2421,137 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Lake Forest, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Developer in Test - SDET</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2074ca8a90ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr, Dev Ops Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Fusable</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Splunk, CI/CD, Jenkins, AWS CodePipeline, Terraform, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642c677020ee17d9</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer Platform</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>American Innovations Ltd</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,199 +2736,199 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfaa8ce7652f89e0</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a6c7bc8bfe481d5f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=07e7dfcc20e69935</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,42 +3041,42 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b17154c636f2d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=011b908a044140ed</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Senior AI ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=94702e41333d36e2</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Sr. Software Engineer Platform</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>American Innovations Ltd</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, IAM, Azure, GCP, Scala, Oracle, NoSQL, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,19 +3296,19 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=5dda3a0a022ad659</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Infrastructure &amp; Security Engineer</t>
+          <t>Software Developer in Test - SDET</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>McAfee</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3317,46 +3317,46 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, RDS, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7691aaaa57c20cab</t>
+          <t>https://www.indeed.com/viewjob?jk=ff2074ca8a90ba86</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,452 +3401,452 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ibotta</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Spark, Scala, Snowflake, ETL, dbt, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815abb92a33544f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Neuberger Berman</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Redwood, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Tools and Automation Engineer – Qualcomm Custom CPU Post-Silicon Team</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=9c5ff0af449554b0</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Systems Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Fountain House</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3787de0a39dc88</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior AI Software Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Support Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Sumitomo Group</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ERP &amp; Database Systems Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Missouri State University</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Enterprise Data Consultant II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>M&amp;T Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,89 +3996,89 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+          <t>https://www.indeed.com/viewjob?jk=5199791c8fddbb8e</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chevy Chase, MD, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FDE-Priniciple Software Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4087,11 +4087,11 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,77 +4101,707 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DLRdmv</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>Java AI / ML Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>(USA) Senior, Data Scientist</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sam's Club</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Bentonville, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Software Engineer (Java)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Englewood, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Évora, P07, PT USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Application Security Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise | HPE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Spring, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ffe5f038b0ab7a88</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Data Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Fountain House</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd3787de0a39dc88</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>FDE-Priniciple Software Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Newpage Digital Healthcare solutions</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Support Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Sumitomo Group</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ERP &amp; Database Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Missouri State University</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Springfield, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Emerson</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>DLRdmv</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
           <t>Teradata Developer-2</t>
         </is>
       </c>
-      <c r="B107" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>Realign</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t>Plano, TX, US USA</t>
         </is>
       </c>
-      <c r="D107" t="n">
+      <c r="D119" t="n">
         <v>10.4</v>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Engineer II - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Chevy Chase, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Commercial Operations BI Analyst (171972)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Piscataway, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-03-10.xlsx
+++ b/results/job_matches_2026-03-10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G125"/>
+  <dimension ref="A1:G112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer Mid-Senior</t>
+          <t>Solution Engineer Prin</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lake, MS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, API Gateway, ECS</t>
+          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea838393bd67f5a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solution Engineer Prin</t>
+          <t>Senior Cloud Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Tanaq Support Services LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, ECS, RDS, Azure, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e894e9507fed28a1</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tanaq Support Services LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41759ea503cef4</t>
+          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b27a9b186a474fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9886af86e7b8bb37</t>
+          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud Engineer III</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,94 +986,94 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38a5d873cb84d03f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevSecOps Engineer - Vilnius, Lithuania</t>
+          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Azure, Blob Storage</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f293139b417c7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Step Functions, S3, ECS, Spark, Spark Streaming</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bbd2619eccd90c81</t>
+          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Servco Pacific Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Honolulu, HI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MySQL</t>
+          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c349face95a4a45</t>
+          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Intelligent Foundations and Experiences)</t>
+          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dabbaca4ff73277</t>
+          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NEP GROUP</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,139 +1151,139 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Scala, MLOps</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0baa9cae1d61c25</t>
+          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer- Databricks</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Servco Pacific Inc.</t>
+          <t>Risepoint</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Honolulu, HI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, dbt, DataOps, CI/CD</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e9c606ecdec1b48</t>
+          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II - (DevOps, SRE &amp; AI)</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Databricks, GCP, Vertex AI, Scala, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f095ee7f910fabf1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NEP GROUP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, Databricks Lakehouse, ELT, dbt</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7aaae7263eeb006</t>
+          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer- Databricks</t>
+          <t>Microsoft Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Risepoint</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7807840cf148c6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, Google Cloud Platform, Cloud Storage, Hadoop, Hive, Spark, Scala, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e03ac8cd61ea5ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Platform Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>HUB International</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, S3, IAM, RDS, Databricks, Spark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fbd5a3a9b84ea86</t>
+          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9912d9da4bc3f6</t>
+          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15de236d284aa16a</t>
+          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b620cd8d63ddbf75</t>
+          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a85a9f5505253398</t>
+          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eda4e4897a5adf7</t>
+          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18838be1c99cbb40</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9971a10c736a11</t>
+          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charleston, SC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12494d85ae71b59c</t>
+          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charleston, SC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d711ce03afe5a4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da07496d01e9d590</t>
+          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431102bf2a9e0130</t>
+          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b176f8ae41728e09</t>
+          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Developer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HUB International</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,84 +1826,84 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55a968a6102e9765</t>
+          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Microsoft Threat Intelligence Analyst</t>
+          <t>Data Engineer, Palo Alto</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Rhombus Power</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee1e4288d005d527</t>
+          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer (Full Stack - Java/Spring Boot, Cassandra)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, Kafka, Oracle, SQL Server, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d529213cb7c025f</t>
+          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Athena, S3, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93ca4121053801b5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer, Palo Alto</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Rhombus Power</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, HBase, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac94ef503754abe1</t>
+          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=30f7a74cbba4893f</t>
+          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Snowflake Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qode</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e1d41e152f0e716</t>
+          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d79bb43a0b28a6f</t>
+          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64cbf6b052467d10</t>
+          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Snowflake Data Architect</t>
+          <t>Cloud Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>27Global</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Leawood, KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375102c1b498bb65</t>
+          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>HHAeXchange</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cb95b007fc606bd</t>
+          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Platform Engineer II (Databricks)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Aledade, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Databricks, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3513e36673430c38</t>
+          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>AWS Java Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>27Global</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Leawood, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,17 +2236,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393333a43b4ec747</t>
+          <t>https://www.indeed.com/viewjob?jk=a24b1c6ccb2c07f0</t>
         </is>
       </c>
     </row>
@@ -2258,12 +2258,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HHAeXchange</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dd040a8fece5606</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer II (Databricks)</t>
+          <t>Business Analyst III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Aledade, Inc.</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db005e0c4338e51a</t>
+          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Viaplus By VINCI Highways</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Hive, Scala, Snowflake, SQL Server, ETL, dbt</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae8f1c950d3e284</t>
+          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Analyst III</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>SoundThinking</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Tucson, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,77 +2376,77 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8973cf57e35678fd</t>
+          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Viaplus By VINCI Highways</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9d5abffe915dc59</t>
+          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SoundThinking</t>
+          <t>Fuse Engineering</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tucson, AZ, US USA</t>
+          <t>Gambrills, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,59 +2456,59 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=704d552d624fa562</t>
+          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Data Engineer, Alteryx/Tableau</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Lake Forest, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bd6a62456b6b177</t>
+          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Tidal Financial Group</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f39136a88bf098e3</t>
+          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Saviynt Integration Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fuse Engineering</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Gambrills, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hadoop, HDFS, Hive, HBase, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39bc34020d288c37</t>
+          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Alteryx/Tableau</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Stirista</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Data Modeling, Talend, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88fd5d251644693f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tidal Financial Group</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Step Functions, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82bf7ea7a30e187</t>
+          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Saviynt Integration Engineer</t>
+          <t>Senior Officer, Data Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Gates Foundation</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Azure, Google Cloud Platform, BigQuery, Cloud Storage</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=259d2046a13c7da4</t>
+          <t>https://www.indeed.com/viewjob?jk=c2bda2dde8a58928</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Stirista</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, SQL Server, Dimensional Modeling</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a3575b03f57d</t>
+          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr Advanced Software Engineer - (DevOps, SRE &amp; AI)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,42 +2726,42 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f865de25337be196</t>
+          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Turaho Business Solutions Private Limited</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfaa8ce7652f89e0</t>
+          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
         </is>
       </c>
     </row>
@@ -2783,20 +2783,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Infosys</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6c7bc8bfe481d5f</t>
+          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Qode</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Glue, Kinesis, Spark, PySpark, Scala, Kafka, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07e7dfcc20e69935</t>
+          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Engineer</t>
+          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=086c7dc6031c17cf</t>
+          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa4527f3f16e08b7</t>
+          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2923,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Turaho Business Solutions Private Limited</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a21232624e7753b</t>
+          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Infosys</t>
+          <t>Barclays</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Whippany, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Sqoop, HBase, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67c855b740d44093</t>
+          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d788a607fee36887</t>
+          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Back End (Java, Python, Spark, Kafka, Scala, Pandas)</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e93e214d4dad1148</t>
+          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b1f065861ef9891</t>
+          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Scala, Snowflake, PostgreSQL, Data Modeling, ETL, ELT, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=224ec9c15578245b</t>
+          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Barclays</t>
+          <t>Baker Tilly</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Whippany, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, ECS, RDS, Databricks, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b21501cda3830ee4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote Nationwide or Hybrid in MN or DC</t>
+          <t>Insights Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Casey's</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Ankeny, IA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af4b17154c636f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AI ML Engineer - Remote</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Penn Mutual</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94702e41333d36e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Developer in Test - SDET</t>
+          <t>Sr IT Analyst - ETL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>McAfee</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff2074ca8a90ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Engineer - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8ced2557d40f2d</t>
+          <t>https://www.indeed.com/viewjob?jk=af4b17154c636f2d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior AI ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,112 +3391,112 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Vertex AI, MLOps, MLflow, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d862a43f9b80b8</t>
+          <t>https://www.indeed.com/viewjob?jk=94702e41333d36e2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69f12a7013ee53a2</t>
+          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>PA Consulting</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=071c7a2aa93a8607</t>
+          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Baker Tilly</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4fe83c271e5bb6</t>
+          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Insights Analyst</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Casey's</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ankeny, IA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, BigQuery, Spark, PySpark, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de4de58fc1657eaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr IT Analyst - ETL</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Informatica PowerCenter, Oracle, Data Modeling, Fact Tables, Dimension Tables, ETL</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9483aa3bee625163</t>
+          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Penn Mutual</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Maven, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,94 +3611,94 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5bbaf07c7108a53</t>
+          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Quantitative Developer / Analytics &amp; Dashboard Engineer</t>
+          <t>Senior Cloud IAM Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Neuberger Berman</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Redwood, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7f5a8a12eb26d2e</t>
+          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tools and Automation Engineer – Qualcomm Custom CPU Post-Silicon Team</t>
+          <t>Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>giftHEALTH</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c5ff0af449554b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist/Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f402e50653896a9</t>
+          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PA Consulting</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Snowflake, Kimball, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00868aa50e72df5</t>
+          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>TomorrowNow</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303b1186f91903b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CAMP Facility Services</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,24 +3811,24 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8759818959e2321</t>
+          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Java AI / ML Integration Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5672dfd6efc5a529</t>
+          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>(USA) Senior, Data Scientist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sam's Club</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bentonville, AR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,102 +3891,102 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39c4848a645662a2</t>
+          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Cloud IAM Engineer</t>
+          <t>Software Engineer (Java)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40a603c9f816d1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Engineer</t>
+          <t>Security Software Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>giftHEALTH</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Scala, CI/CD, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, DynamoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b9aa0dc8710174</t>
+          <t>https://www.indeed.com/viewjob?jk=86f57988374a8d78</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Enterprise Data Consultant II</t>
+          <t>Senior AI Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>M&amp;T Bank</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Scala, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5199791c8fddbb8e</t>
+          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Scientist/Engineer</t>
+          <t>Data Support Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Sumitomo Group</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, ETL, Power BI, Tableau, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c30c612381f20d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Java/SpringBoot - Remote</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Scala, Kafka, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd81d8c7e68747d</t>
+          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform &amp; Agentic Systems</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>TomorrowNow</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes, pytest</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,67 +4101,67 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b91ce245792f05e</t>
+          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>CAMP Facility Services</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee233f823233f90</t>
+          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Java AI / ML Integration Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chevy Chase, MD, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=255e0389c228b0d3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>(USA) Senior, Data Scientist</t>
+          <t>FDE-Priniciple Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sam's Club</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bentonville, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, Spark, Scala, Data Modeling, Power BI, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76bbb3d91cd5fb8b</t>
+          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer (Java)</t>
+          <t>Commercial Operations BI Analyst (171972)</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, RDS, Scala, Kafka, Oracle, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a683bae04b939136</t>
+          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Évora, P07, PT USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, NoSQL, Data Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31401d66cdf3de8c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Application Security Engineer</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>DLRdmv</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spring, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Jenkins</t>
+          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffe5f038b0ab7a88</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Enterprise Data Scientist – Human Capital</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CHS Corporate</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,472 +4336,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Snowflake, Oracle, SQL Server, MLOps, MLflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5b74bfc1321d7cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Data Systems Analyst</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Fountain House</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Dataflow, Scala, SQL Server, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd3787de0a39dc88</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>FDE-Priniciple Software Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Newpage Digital Healthcare solutions</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b726ef965a254459</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Support Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Sumitomo Group</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, PySpark, Scala, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbe5f42d96cfbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>ERP &amp; Database Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Missouri State University</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Springfield, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, CI/CD, Terraform, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83e2028b144ba779</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Senior AI Software Engineer</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Emerson</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Snowflake, Oracle, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=34496d8f0b690b06</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>SQL Developer</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>DLRdmv</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL, ETL, ELT, Airflow</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8998a9e422195b</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Teradata Developer-2</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Realign</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, Sqoop, Impala, Spark, PySpark, Kafka, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5a5babd5b8f9d05b</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Solution Architect</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>HCA Healthcare</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Hive, Scala, Data Modeling, Splunk, CI/CD</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22287aabfece036a</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, SQL Server, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3cc16dd8a70e8cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d93e330f569c8606</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8115e661d8a325c</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Engineer II - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Chevy Chase, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6998f845af080a70</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Commercial Operations BI Analyst (171972)</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Colgate-Palmolive</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Piscataway, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, BigQuery, Scala, Snowflake, Data Modeling, Tableau, MS Excel, Python</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=84435ef31a96cb32</t>
+          <t>https://www.indeed.com/viewjob?jk=4bbf4b674bc99f7c</t>
         </is>
       </c>
     </row>
